--- a/existing_customer/files/account_summary.xlsx
+++ b/existing_customer/files/account_summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sumandeep.a.kaur\Documents\B2B Agentic Screens Demo - Existing Customers\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhilasha.anand\b2b_streamlit_apps\acquisition\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1B402A0-6A43-4922-9CBC-CBDF3BB165D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA2620FB-CD4C-439B-BCAB-1100A6850B2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Account Overview" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="252">
   <si>
     <t>Customer 360° — Account Summary</t>
   </si>
@@ -535,15 +535,6 @@
   </si>
   <si>
     <t>Domain_3_Top_Keywords (Top 5)</t>
-  </si>
-  <si>
-    <t>SD-WAN optimisation, Ethernet networking, bandwidth expansion, network modernisation, site connectivity</t>
-  </si>
-  <si>
-    <t>IoT networks, asset monitoring, edge connectivity, device management, remote telemetry</t>
-  </si>
-  <si>
-    <t>network security, secure SD-WAN, threat protection, firewall upgrades, perimeter security</t>
   </si>
   <si>
     <t>Telecommunications infrastructure, network resilience, high-availability networks, carrier diversity, core networking</t>
@@ -852,6 +843,27 @@
   </si>
   <si>
     <t>Yes</t>
+  </si>
+  <si>
+    <t>Network Infrastructure</t>
+  </si>
+  <si>
+    <t>IoT &amp; Asset Management</t>
+  </si>
+  <si>
+    <t>AI &amp; Automation</t>
+  </si>
+  <si>
+    <t>Construction AI solutions, Site safety automation, AI workforce scheduling, Computer vision construction</t>
+  </si>
+  <si>
+    <t>Equipment monitoring systems, Heavy equipment fleet management, Construction IoT telemetry, Asset tracking systems, Fleet telematics</t>
+  </si>
+  <si>
+    <t>Bandwidth expansion, Ethernet networking, SD-WAN optimization</t>
+  </si>
+  <si>
+    <t>Digital Transformation</t>
   </si>
 </sst>
 </file>
@@ -1164,12 +1176,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1182,6 +1188,12 @@
     <xf numFmtId="49" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -1486,13 +1498,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" customWidth="1"/>
+    <col min="1" max="1" width="16.88671875" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="57.5703125" customWidth="1"/>
+    <col min="5" max="5" width="57.5546875" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
@@ -1505,43 +1517,43 @@
     <col min="15" max="15" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+    <row r="1" spans="1:15" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-    </row>
-    <row r="2" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="35" t="s">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
+    </row>
+    <row r="2" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36"/>
-      <c r="M2" s="36"/>
-      <c r="N2" s="36"/>
-    </row>
-    <row r="4" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="40"/>
+    </row>
+    <row r="4" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -1588,7 +1600,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>156</v>
       </c>
@@ -1635,7 +1647,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>28</v>
       </c>
@@ -1682,7 +1694,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>39</v>
       </c>
@@ -1729,7 +1741,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>49</v>
       </c>
@@ -1776,7 +1788,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>57</v>
       </c>
@@ -1823,7 +1835,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>67</v>
       </c>
@@ -1870,7 +1882,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>76</v>
       </c>
@@ -1917,7 +1929,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>82</v>
       </c>
@@ -1964,7 +1976,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>155</v>
       </c>
@@ -2011,7 +2023,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>96</v>
       </c>
@@ -2070,41 +2082,41 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
-    <col min="4" max="12" width="36.7109375" customWidth="1"/>
+    <col min="4" max="12" width="36.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="32.1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="38" t="s">
+    <row r="1" spans="1:12" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="42" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-    </row>
-    <row r="2" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="35" t="s">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+    </row>
+    <row r="2" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="39" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-    </row>
-    <row r="4" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+    </row>
+    <row r="4" spans="1:12" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -2139,7 +2151,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>156</v>
       </c>
@@ -2150,19 +2162,19 @@
         <v>117</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>118</v>
+        <v>245</v>
       </c>
       <c r="E5" s="4">
         <v>85</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>119</v>
+        <v>246</v>
       </c>
       <c r="G5" s="4">
         <v>72</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>120</v>
+        <v>247</v>
       </c>
       <c r="I5" s="4">
         <v>68</v>
@@ -2174,7 +2186,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>28</v>
       </c>
@@ -2209,7 +2221,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>39</v>
       </c>
@@ -2244,7 +2256,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>49</v>
       </c>
@@ -2279,7 +2291,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>57</v>
       </c>
@@ -2314,7 +2326,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>67</v>
       </c>
@@ -2349,7 +2361,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>76</v>
       </c>
@@ -2384,7 +2396,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>82</v>
       </c>
@@ -2419,7 +2431,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>155</v>
       </c>
@@ -2454,7 +2466,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>96</v>
       </c>
@@ -2489,7 +2501,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D16" s="13" t="s">
         <v>157</v>
       </c>
@@ -2518,36 +2530,36 @@
         <v>165</v>
       </c>
     </row>
-    <row r="17" spans="4:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D17" s="14" t="s">
-        <v>118</v>
+        <v>245</v>
       </c>
       <c r="E17" s="14">
         <v>85</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>166</v>
+        <v>250</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>119</v>
+        <v>246</v>
       </c>
       <c r="H17" s="14">
         <v>72</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>167</v>
+        <v>249</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>120</v>
+        <v>247</v>
       </c>
       <c r="K17" s="14">
         <v>68</v>
       </c>
       <c r="L17" s="14" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="18" spans="4:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="18" spans="4:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D18" s="15"/>
       <c r="E18" s="15"/>
       <c r="F18" s="15"/>
@@ -2558,7 +2570,7 @@
       <c r="K18" s="15"/>
       <c r="L18" s="15"/>
     </row>
-    <row r="19" spans="4:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D19" s="15" t="s">
         <v>126</v>
       </c>
@@ -2566,7 +2578,7 @@
         <v>90</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G19" s="15" t="s">
         <v>120</v>
@@ -2575,7 +2587,7 @@
         <v>86</v>
       </c>
       <c r="I19" s="15" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>127</v>
@@ -2584,10 +2596,10 @@
         <v>80</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="20" spans="4:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="20" spans="4:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D20" s="15" t="s">
         <v>130</v>
       </c>
@@ -2595,7 +2607,7 @@
         <v>75</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G20" s="15" t="s">
         <v>118</v>
@@ -2604,7 +2616,7 @@
         <v>68</v>
       </c>
       <c r="I20" s="15" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="J20" s="15" t="s">
         <v>120</v>
@@ -2613,10 +2625,10 @@
         <v>62</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="21" spans="4:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="21" spans="4:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
       <c r="F21" s="15"/>
@@ -2627,7 +2639,7 @@
       <c r="K21" s="15"/>
       <c r="L21" s="15"/>
     </row>
-    <row r="22" spans="4:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="4:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D22" s="15" t="s">
         <v>126</v>
       </c>
@@ -2635,7 +2647,7 @@
         <v>94</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G22" s="15" t="s">
         <v>134</v>
@@ -2644,7 +2656,7 @@
         <v>90</v>
       </c>
       <c r="I22" s="15" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="J22" s="15" t="s">
         <v>120</v>
@@ -2653,10 +2665,10 @@
         <v>88</v>
       </c>
       <c r="L22" s="15" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="23" spans="4:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="23" spans="4:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D23" s="15" t="s">
         <v>118</v>
       </c>
@@ -2664,7 +2676,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G23" s="15"/>
       <c r="H23" s="15"/>
@@ -2673,7 +2685,7 @@
       <c r="K23" s="15"/>
       <c r="L23" s="15"/>
     </row>
-    <row r="24" spans="4:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="4:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D24" s="15"/>
       <c r="E24" s="15"/>
       <c r="F24" s="15"/>
@@ -2684,7 +2696,7 @@
       <c r="K24" s="15"/>
       <c r="L24" s="15"/>
     </row>
-    <row r="25" spans="4:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="4:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D25" s="15" t="s">
         <v>119</v>
       </c>
@@ -2692,7 +2704,7 @@
         <v>82</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G25" s="15" t="s">
         <v>118</v>
@@ -2701,7 +2713,7 @@
         <v>74</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="J25" s="15" t="s">
         <v>138</v>
@@ -2710,10 +2722,10 @@
         <v>70</v>
       </c>
       <c r="L25" s="15" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="26" spans="4:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="26" spans="4:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D26" s="15"/>
       <c r="E26" s="15"/>
       <c r="F26" s="15"/>
@@ -2735,13 +2747,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACAA242C-34EE-4A9A-AF24-9E3D0B068461}">
-  <dimension ref="A1:AJ26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AK26"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="32" width="27.7109375" customWidth="1"/>
+    <col min="1" max="32" width="27.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:37" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
         <v>2</v>
       </c>
@@ -2791,7 +2803,7 @@
         <v>108</v>
       </c>
       <c r="Q1" s="16" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="R1" s="16" t="s">
         <v>109</v>
@@ -2800,7 +2812,7 @@
         <v>110</v>
       </c>
       <c r="T1" s="16" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="U1" s="16" t="s">
         <v>111</v>
@@ -2809,7 +2821,7 @@
         <v>112</v>
       </c>
       <c r="W1" s="16" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="X1" s="16" t="s">
         <v>113</v>
@@ -2818,13 +2830,13 @@
         <v>114</v>
       </c>
       <c r="Z1" s="16" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="AA1" s="26" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="AB1" s="29" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AC1" s="26" t="s">
         <v>115</v>
@@ -2850,8 +2862,11 @@
       <c r="AJ1" s="16" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="2" spans="1:36" ht="48" x14ac:dyDescent="0.25">
+      <c r="AK1" s="1" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="2" spans="1:37" ht="57" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="s">
         <v>156</v>
       </c>
@@ -2886,10 +2901,10 @@
         <v>23</v>
       </c>
       <c r="L2" s="18" t="s">
-        <v>236</v>
-      </c>
-      <c r="M2" s="41" t="s">
-        <v>246</v>
+        <v>233</v>
+      </c>
+      <c r="M2" s="37" t="s">
+        <v>243</v>
       </c>
       <c r="N2" s="18" t="s">
         <v>26</v>
@@ -2901,40 +2916,40 @@
         <v>117</v>
       </c>
       <c r="Q2" s="18" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="R2" s="18" t="s">
-        <v>118</v>
+        <v>245</v>
       </c>
       <c r="S2" s="18">
         <v>85</v>
       </c>
       <c r="T2" s="18" t="s">
-        <v>166</v>
+        <v>250</v>
       </c>
       <c r="U2" s="18" t="s">
-        <v>119</v>
+        <v>246</v>
       </c>
       <c r="V2" s="18">
         <v>72</v>
       </c>
       <c r="W2" s="18" t="s">
-        <v>167</v>
+        <v>249</v>
       </c>
       <c r="X2" s="18" t="s">
-        <v>120</v>
+        <v>247</v>
       </c>
       <c r="Y2" s="18">
         <v>68</v>
       </c>
       <c r="Z2" s="18" t="s">
-        <v>168</v>
+        <v>248</v>
       </c>
       <c r="AA2" s="27" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="AB2" s="30" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="AC2" s="27" t="s">
         <v>23</v>
@@ -2960,8 +2975,11 @@
       <c r="AJ2" s="20" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK2" s="21" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="s">
         <v>28</v>
       </c>
@@ -2996,9 +3014,9 @@
         <v>35</v>
       </c>
       <c r="L3" s="17" t="s">
-        <v>237</v>
-      </c>
-      <c r="M3" s="41" t="s">
+        <v>234</v>
+      </c>
+      <c r="M3" s="37" t="s">
         <v>37</v>
       </c>
       <c r="N3" s="17" t="s">
@@ -3033,10 +3051,10 @@
       </c>
       <c r="Z3" s="17"/>
       <c r="AA3" s="28" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="AB3" s="31" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AC3" s="28" t="s">
         <v>35</v>
@@ -3062,8 +3080,11 @@
       <c r="AJ3" s="17" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="4" spans="1:36" ht="60" x14ac:dyDescent="0.25">
+      <c r="AK3" s="17" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
         <v>39</v>
       </c>
@@ -3098,9 +3119,9 @@
         <v>35</v>
       </c>
       <c r="L4" s="18" t="s">
-        <v>238</v>
-      </c>
-      <c r="M4" s="41" t="s">
+        <v>235</v>
+      </c>
+      <c r="M4" s="37" t="s">
         <v>47</v>
       </c>
       <c r="N4" s="18" t="s">
@@ -3113,7 +3134,7 @@
         <v>125</v>
       </c>
       <c r="Q4" s="18" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="R4" s="18" t="s">
         <v>126</v>
@@ -3122,7 +3143,7 @@
         <v>90</v>
       </c>
       <c r="T4" s="18" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="U4" s="18" t="s">
         <v>120</v>
@@ -3131,7 +3152,7 @@
         <v>86</v>
       </c>
       <c r="W4" s="18" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="X4" s="18" t="s">
         <v>127</v>
@@ -3140,13 +3161,13 @@
         <v>80</v>
       </c>
       <c r="Z4" s="18" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="AA4" s="27" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="AB4" s="30" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="AC4" s="27" t="s">
         <v>27</v>
@@ -3172,8 +3193,11 @@
       <c r="AJ4" s="18" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="5" spans="1:36" ht="48" x14ac:dyDescent="0.25">
+      <c r="AK4" s="17" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
         <v>49</v>
       </c>
@@ -3208,9 +3232,9 @@
         <v>35</v>
       </c>
       <c r="L5" s="17" t="s">
-        <v>239</v>
-      </c>
-      <c r="M5" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="M5" s="38" t="s">
         <v>56</v>
       </c>
       <c r="N5" s="17" t="s">
@@ -3223,7 +3247,7 @@
         <v>129</v>
       </c>
       <c r="Q5" s="17" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="R5" s="17" t="s">
         <v>130</v>
@@ -3232,7 +3256,7 @@
         <v>75</v>
       </c>
       <c r="T5" s="17" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="U5" s="17" t="s">
         <v>118</v>
@@ -3241,7 +3265,7 @@
         <v>68</v>
       </c>
       <c r="W5" s="17" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="X5" s="17" t="s">
         <v>120</v>
@@ -3250,13 +3274,13 @@
         <v>62</v>
       </c>
       <c r="Z5" s="17" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="AA5" s="28" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="AB5" s="31" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="AC5" s="28" t="s">
         <v>23</v>
@@ -3282,8 +3306,11 @@
       <c r="AJ5" s="17" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK5" s="17" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
         <v>57</v>
       </c>
@@ -3318,9 +3345,9 @@
         <v>64</v>
       </c>
       <c r="L6" s="18" t="s">
-        <v>240</v>
-      </c>
-      <c r="M6" s="41" t="s">
+        <v>237</v>
+      </c>
+      <c r="M6" s="37" t="s">
         <v>37</v>
       </c>
       <c r="N6" s="18" t="s">
@@ -3355,10 +3382,10 @@
       </c>
       <c r="Z6" s="18"/>
       <c r="AA6" s="27" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="AB6" s="30" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="AC6" s="27" t="s">
         <v>64</v>
@@ -3382,10 +3409,13 @@
         <v>124</v>
       </c>
       <c r="AJ6" s="24" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="7" spans="1:36" ht="48" x14ac:dyDescent="0.25">
+        <v>244</v>
+      </c>
+      <c r="AK6" s="17" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
         <v>67</v>
       </c>
@@ -3420,9 +3450,9 @@
         <v>23</v>
       </c>
       <c r="L7" s="17" t="s">
-        <v>241</v>
-      </c>
-      <c r="M7" s="42" t="s">
+        <v>238</v>
+      </c>
+      <c r="M7" s="38" t="s">
         <v>74</v>
       </c>
       <c r="N7" s="17" t="s">
@@ -3435,7 +3465,7 @@
         <v>133</v>
       </c>
       <c r="Q7" s="17" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="R7" s="17" t="s">
         <v>126</v>
@@ -3444,7 +3474,7 @@
         <v>94</v>
       </c>
       <c r="T7" s="17" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="U7" s="17" t="s">
         <v>134</v>
@@ -3453,7 +3483,7 @@
         <v>90</v>
       </c>
       <c r="W7" s="17" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="X7" s="17" t="s">
         <v>120</v>
@@ -3462,13 +3492,13 @@
         <v>88</v>
       </c>
       <c r="Z7" s="17" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AA7" s="28" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="AB7" s="31" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="AC7" s="28" t="s">
         <v>27</v>
@@ -3494,8 +3524,11 @@
       <c r="AJ7" s="17" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="8" spans="1:36" ht="48" x14ac:dyDescent="0.25">
+      <c r="AK7" s="17" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
         <v>76</v>
       </c>
@@ -3530,9 +3563,9 @@
         <v>35</v>
       </c>
       <c r="L8" s="18" t="s">
-        <v>243</v>
-      </c>
-      <c r="M8" s="41" t="s">
+        <v>240</v>
+      </c>
+      <c r="M8" s="37" t="s">
         <v>56</v>
       </c>
       <c r="N8" s="18" t="s">
@@ -3552,7 +3585,7 @@
         <v>60</v>
       </c>
       <c r="T8" s="18" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="U8" s="18" t="s">
         <v>124</v>
@@ -3569,10 +3602,10 @@
       </c>
       <c r="Z8" s="18"/>
       <c r="AA8" s="27" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="AB8" s="30" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="AC8" s="27" t="s">
         <v>35</v>
@@ -3598,8 +3631,11 @@
       <c r="AJ8" s="18" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="9" spans="1:36" ht="24" x14ac:dyDescent="0.25">
+      <c r="AK8" s="17" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
         <v>82</v>
       </c>
@@ -3634,9 +3670,9 @@
         <v>35</v>
       </c>
       <c r="L9" s="17" t="s">
-        <v>242</v>
-      </c>
-      <c r="M9" s="42" t="s">
+        <v>239</v>
+      </c>
+      <c r="M9" s="38" t="s">
         <v>47</v>
       </c>
       <c r="N9" s="17" t="s">
@@ -3649,7 +3685,7 @@
         <v>135</v>
       </c>
       <c r="Q9" s="17" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="R9" s="17" t="s">
         <v>124</v>
@@ -3673,10 +3709,10 @@
       </c>
       <c r="Z9" s="17"/>
       <c r="AA9" s="28" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="AB9" s="31" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="AC9" s="28" t="s">
         <v>35</v>
@@ -3702,8 +3738,11 @@
       <c r="AJ9" s="17" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="10" spans="1:36" ht="48" x14ac:dyDescent="0.25">
+      <c r="AK9" s="17" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" spans="1:37" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
         <v>155</v>
       </c>
@@ -3738,9 +3777,9 @@
         <v>23</v>
       </c>
       <c r="L10" s="18" t="s">
-        <v>244</v>
-      </c>
-      <c r="M10" s="41" t="s">
+        <v>241</v>
+      </c>
+      <c r="M10" s="37" t="s">
         <v>94</v>
       </c>
       <c r="N10" s="18" t="s">
@@ -3753,7 +3792,7 @@
         <v>137</v>
       </c>
       <c r="Q10" s="18" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="R10" s="18" t="s">
         <v>119</v>
@@ -3762,7 +3801,7 @@
         <v>82</v>
       </c>
       <c r="T10" s="18" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="U10" s="18" t="s">
         <v>118</v>
@@ -3771,7 +3810,7 @@
         <v>74</v>
       </c>
       <c r="W10" s="18" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="X10" s="18" t="s">
         <v>138</v>
@@ -3780,13 +3819,13 @@
         <v>70</v>
       </c>
       <c r="Z10" s="18" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="AA10" s="27" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="AB10" s="30" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="AC10" s="27" t="s">
         <v>23</v>
@@ -3812,8 +3851,11 @@
       <c r="AJ10" s="20" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="11" spans="1:36" ht="24" x14ac:dyDescent="0.25">
+      <c r="AK10" s="17" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A11" s="17" t="s">
         <v>96</v>
       </c>
@@ -3848,9 +3890,9 @@
         <v>64</v>
       </c>
       <c r="L11" s="17" t="s">
-        <v>245</v>
-      </c>
-      <c r="M11" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="M11" s="38" t="s">
         <v>37</v>
       </c>
       <c r="N11" s="17" t="s">
@@ -3885,10 +3927,10 @@
       </c>
       <c r="Z11" s="17"/>
       <c r="AA11" s="28" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="AB11" s="31" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="AC11" s="28" t="s">
         <v>105</v>
@@ -3914,104 +3956,107 @@
       <c r="AJ11" s="17" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="K13" s="39"/>
-      <c r="L13" s="39"/>
-      <c r="M13" s="39"/>
-      <c r="N13" s="39"/>
-      <c r="O13" s="39"/>
-    </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="K14" s="39"/>
-      <c r="L14" s="39"/>
-      <c r="M14" s="39"/>
-      <c r="N14" s="39"/>
-      <c r="O14" s="39"/>
-    </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="K15" s="39"/>
-      <c r="L15" s="39"/>
-      <c r="M15" s="39"/>
-      <c r="N15" s="39"/>
-      <c r="O15" s="40"/>
-    </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="K16" s="39"/>
-      <c r="L16" s="39"/>
-      <c r="M16" s="39"/>
-      <c r="N16" s="39"/>
-      <c r="O16" s="40"/>
-    </row>
-    <row r="17" spans="11:15" x14ac:dyDescent="0.25">
-      <c r="K17" s="39"/>
-      <c r="L17" s="39"/>
-      <c r="M17" s="39"/>
-      <c r="N17" s="39"/>
-      <c r="O17" s="40"/>
-    </row>
-    <row r="18" spans="11:15" x14ac:dyDescent="0.25">
-      <c r="K18" s="39"/>
-      <c r="L18" s="39"/>
-      <c r="M18" s="39"/>
-      <c r="N18" s="39"/>
-      <c r="O18" s="40"/>
-    </row>
-    <row r="19" spans="11:15" x14ac:dyDescent="0.25">
-      <c r="K19" s="39"/>
-      <c r="L19" s="39"/>
-      <c r="M19" s="39"/>
-      <c r="N19" s="39"/>
-      <c r="O19" s="40"/>
-    </row>
-    <row r="20" spans="11:15" x14ac:dyDescent="0.25">
-      <c r="K20" s="39"/>
-      <c r="L20" s="39"/>
-      <c r="M20" s="39"/>
-      <c r="N20" s="39"/>
-      <c r="O20" s="40"/>
-    </row>
-    <row r="21" spans="11:15" x14ac:dyDescent="0.25">
-      <c r="K21" s="39"/>
-      <c r="L21" s="39"/>
-      <c r="M21" s="39"/>
-      <c r="N21" s="39"/>
-      <c r="O21" s="40"/>
-    </row>
-    <row r="22" spans="11:15" x14ac:dyDescent="0.25">
-      <c r="K22" s="39"/>
-      <c r="L22" s="39"/>
-      <c r="M22" s="39"/>
-      <c r="N22" s="39"/>
-      <c r="O22" s="40"/>
-    </row>
-    <row r="23" spans="11:15" x14ac:dyDescent="0.25">
-      <c r="K23" s="39"/>
-      <c r="L23" s="39"/>
-      <c r="M23" s="39"/>
-      <c r="N23" s="39"/>
-      <c r="O23" s="40"/>
-    </row>
-    <row r="24" spans="11:15" x14ac:dyDescent="0.25">
-      <c r="K24" s="39"/>
-      <c r="L24" s="39"/>
-      <c r="M24" s="39"/>
-      <c r="N24" s="39"/>
-      <c r="O24" s="40"/>
-    </row>
-    <row r="25" spans="11:15" x14ac:dyDescent="0.25">
-      <c r="K25" s="39"/>
-      <c r="L25" s="39"/>
-      <c r="M25" s="39"/>
-      <c r="N25" s="39"/>
-      <c r="O25" s="39"/>
-    </row>
-    <row r="26" spans="11:15" x14ac:dyDescent="0.25">
-      <c r="K26" s="39"/>
-      <c r="L26" s="39"/>
-      <c r="M26" s="39"/>
-      <c r="N26" s="39"/>
-      <c r="O26" s="39"/>
+      <c r="AK11" s="17" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="K13" s="35"/>
+      <c r="L13" s="35"/>
+      <c r="M13" s="35"/>
+      <c r="N13" s="35"/>
+      <c r="O13" s="35"/>
+    </row>
+    <row r="14" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="K14" s="35"/>
+      <c r="L14" s="35"/>
+      <c r="M14" s="35"/>
+      <c r="N14" s="35"/>
+      <c r="O14" s="35"/>
+    </row>
+    <row r="15" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="K15" s="35"/>
+      <c r="L15" s="35"/>
+      <c r="M15" s="35"/>
+      <c r="N15" s="35"/>
+      <c r="O15" s="36"/>
+    </row>
+    <row r="16" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="K16" s="35"/>
+      <c r="L16" s="35"/>
+      <c r="M16" s="35"/>
+      <c r="N16" s="35"/>
+      <c r="O16" s="36"/>
+    </row>
+    <row r="17" spans="11:15" x14ac:dyDescent="0.3">
+      <c r="K17" s="35"/>
+      <c r="L17" s="35"/>
+      <c r="M17" s="35"/>
+      <c r="N17" s="35"/>
+      <c r="O17" s="36"/>
+    </row>
+    <row r="18" spans="11:15" x14ac:dyDescent="0.3">
+      <c r="K18" s="35"/>
+      <c r="L18" s="35"/>
+      <c r="M18" s="35"/>
+      <c r="N18" s="35"/>
+      <c r="O18" s="36"/>
+    </row>
+    <row r="19" spans="11:15" x14ac:dyDescent="0.3">
+      <c r="K19" s="35"/>
+      <c r="L19" s="35"/>
+      <c r="M19" s="35"/>
+      <c r="N19" s="35"/>
+      <c r="O19" s="36"/>
+    </row>
+    <row r="20" spans="11:15" x14ac:dyDescent="0.3">
+      <c r="K20" s="35"/>
+      <c r="L20" s="35"/>
+      <c r="M20" s="35"/>
+      <c r="N20" s="35"/>
+      <c r="O20" s="36"/>
+    </row>
+    <row r="21" spans="11:15" x14ac:dyDescent="0.3">
+      <c r="K21" s="35"/>
+      <c r="L21" s="35"/>
+      <c r="M21" s="35"/>
+      <c r="N21" s="35"/>
+      <c r="O21" s="36"/>
+    </row>
+    <row r="22" spans="11:15" x14ac:dyDescent="0.3">
+      <c r="K22" s="35"/>
+      <c r="L22" s="35"/>
+      <c r="M22" s="35"/>
+      <c r="N22" s="35"/>
+      <c r="O22" s="36"/>
+    </row>
+    <row r="23" spans="11:15" x14ac:dyDescent="0.3">
+      <c r="K23" s="35"/>
+      <c r="L23" s="35"/>
+      <c r="M23" s="35"/>
+      <c r="N23" s="35"/>
+      <c r="O23" s="36"/>
+    </row>
+    <row r="24" spans="11:15" x14ac:dyDescent="0.3">
+      <c r="K24" s="35"/>
+      <c r="L24" s="35"/>
+      <c r="M24" s="35"/>
+      <c r="N24" s="35"/>
+      <c r="O24" s="36"/>
+    </row>
+    <row r="25" spans="11:15" x14ac:dyDescent="0.3">
+      <c r="K25" s="35"/>
+      <c r="L25" s="35"/>
+      <c r="M25" s="35"/>
+      <c r="N25" s="35"/>
+      <c r="O25" s="35"/>
+    </row>
+    <row r="26" spans="11:15" x14ac:dyDescent="0.3">
+      <c r="K26" s="35"/>
+      <c r="L26" s="35"/>
+      <c r="M26" s="35"/>
+      <c r="N26" s="35"/>
+      <c r="O26" s="35"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4021,230 +4066,230 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88E46911-9D54-4C99-B80B-AC0680704439}">
   <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="6" width="27.7109375" customWidth="1"/>
+    <col min="1" max="6" width="27.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="B1" s="32" t="s">
+        <v>188</v>
+      </c>
+      <c r="C1" s="32" t="s">
+        <v>189</v>
+      </c>
+      <c r="D1" s="32" t="s">
         <v>190</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="E1" s="32" t="s">
         <v>191</v>
       </c>
-      <c r="C1" s="32" t="s">
+      <c r="F1" s="32" t="s">
         <v>192</v>
       </c>
-      <c r="D1" s="32" t="s">
+    </row>
+    <row r="2" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="34" t="s">
         <v>193</v>
       </c>
-      <c r="E1" s="32" t="s">
+      <c r="B2" s="33" t="s">
         <v>194</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="C2" s="33" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A2" s="34" t="s">
+      <c r="D2" s="33" t="s">
         <v>196</v>
       </c>
-      <c r="B2" s="33" t="s">
+      <c r="E2" s="33" t="s">
         <v>197</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="F2" s="33" t="s">
         <v>198</v>
       </c>
-      <c r="D2" s="33" t="s">
+    </row>
+    <row r="3" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="34" t="s">
         <v>199</v>
       </c>
-      <c r="E2" s="33" t="s">
+      <c r="B3" s="33" t="s">
         <v>200</v>
       </c>
-      <c r="F2" s="33" t="s">
+      <c r="C3" s="33" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A3" s="34" t="s">
+      <c r="D3" s="33" t="s">
         <v>202</v>
       </c>
-      <c r="B3" s="33" t="s">
+      <c r="E3" s="33" t="s">
         <v>203</v>
       </c>
-      <c r="C3" s="33" t="s">
+      <c r="F3" s="33" t="s">
         <v>204</v>
       </c>
-      <c r="D3" s="33" t="s">
+    </row>
+    <row r="4" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="34" t="s">
         <v>205</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="B4" s="34" t="s">
         <v>206</v>
       </c>
-      <c r="F3" s="33" t="s">
+      <c r="C4" s="33" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A4" s="34" t="s">
+      <c r="D4" s="33" t="s">
         <v>208</v>
       </c>
-      <c r="B4" s="34" t="s">
+      <c r="E4" s="33" t="s">
         <v>209</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="F4" s="33" t="s">
         <v>210</v>
       </c>
-      <c r="D4" s="33" t="s">
+    </row>
+    <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="34" t="s">
         <v>211</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="B5" s="33" t="s">
         <v>212</v>
       </c>
-      <c r="F4" s="33" t="s">
+      <c r="C5" s="33" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="34" t="s">
+      <c r="D5" s="33" t="s">
         <v>214</v>
       </c>
-      <c r="B5" s="33" t="s">
+      <c r="E5" s="33" t="s">
         <v>215</v>
       </c>
-      <c r="C5" s="33" t="s">
+      <c r="F5" s="33" t="s">
         <v>216</v>
       </c>
-      <c r="D5" s="33" t="s">
-        <v>217</v>
-      </c>
-      <c r="E5" s="33" t="s">
-        <v>218</v>
-      </c>
-      <c r="F5" s="33" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="32" t="s">
         <v>2</v>
       </c>
       <c r="B10" s="32" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A11" s="34" t="s">
         <v>156</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A12" s="34" t="s">
         <v>28</v>
       </c>
       <c r="B12" s="34" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A13" s="34" t="s">
         <v>39</v>
       </c>
       <c r="B13" s="34" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A14" s="34" t="s">
         <v>49</v>
       </c>
       <c r="B14" s="34" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A15" s="34" t="s">
         <v>57</v>
       </c>
       <c r="B15" s="34" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A16" s="34" t="s">
         <v>67</v>
       </c>
       <c r="B16" s="34" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A17" s="34" t="s">
         <v>76</v>
       </c>
       <c r="B17" s="34" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A18" s="34" t="s">
         <v>82</v>
       </c>
       <c r="B18" s="34" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A19" s="34" t="s">
         <v>155</v>
       </c>
       <c r="B19" s="34" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A20" s="34" t="s">
         <v>96</v>
       </c>
       <c r="B20" s="34" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C20" s="33" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -4254,8 +4299,8 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -4264,33 +4309,34 @@
     <col min="5" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="10" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="9" max="9" width="20.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="32.1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="38" t="s">
+    <row r="1" spans="1:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="42" t="s">
         <v>140</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-    </row>
-    <row r="2" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="35" t="s">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+    </row>
+    <row r="2" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="39" t="s">
         <v>141</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-    </row>
-    <row r="4" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+    </row>
+    <row r="4" spans="1:9" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -4315,8 +4361,11 @@
       <c r="H4" s="1" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I4" s="1" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>156</v>
       </c>
@@ -4341,8 +4390,11 @@
       <c r="H5" s="11" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I5" s="12" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>28</v>
       </c>
@@ -4367,8 +4419,11 @@
       <c r="H6" s="7" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I6" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>39</v>
       </c>
@@ -4393,8 +4448,11 @@
       <c r="H7" s="8" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I7" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>49</v>
       </c>
@@ -4419,8 +4477,11 @@
       <c r="H8" s="7" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I8" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>57</v>
       </c>
@@ -4445,8 +4506,11 @@
       <c r="H9" s="10" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I9" s="8" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>67</v>
       </c>
@@ -4471,8 +4535,11 @@
       <c r="H10" s="7" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I10" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>76</v>
       </c>
@@ -4497,8 +4564,11 @@
       <c r="H11" s="8" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I11" s="8" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>82</v>
       </c>
@@ -4523,8 +4593,11 @@
       <c r="H12" s="7" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I12" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>155</v>
       </c>
@@ -4549,8 +4622,11 @@
       <c r="H13" s="11" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I13" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>96</v>
       </c>
@@ -4573,6 +4649,9 @@
         <v>124</v>
       </c>
       <c r="H14" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="I14" s="7" t="s">
         <v>124</v>
       </c>
     </row>
